--- a/闲鱼用户旅程.xlsx
+++ b/闲鱼用户旅程.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,16 +26,93 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Inter"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Inter"/>
+      <color rgb="001A1A1A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Inter"/>
+      <b val="1"/>
+      <color rgb="00D85A30"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Inter"/>
+      <b val="1"/>
+      <color rgb="001A1A1A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Inter"/>
+      <b val="1"/>
+      <color rgb="003B6D11"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Inter"/>
+      <b val="1"/>
+      <color rgb="00BA7517"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Inter"/>
+      <b val="1"/>
+      <color rgb="00BA7517"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Inter"/>
+      <b val="1"/>
+      <color rgb="00E24B4A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Inter"/>
+      <b val="1"/>
+      <color rgb="000F6E56"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002C2C2A"/>
+        <bgColor rgb="002C2C2A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FAECE7"/>
+        <bgColor rgb="00FAECE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FAEEDA"/>
+        <bgColor rgb="00FAEEDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E1F5EE"/>
+        <bgColor rgb="00E1F5EE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +120,53 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0CDC4"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0CDC4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0CDC4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0CDC4"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,385 +535,385 @@
   <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>阶段区间</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>阶段名称</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>线上行为</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>线下行为</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>触点/渠道</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>用户想法</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>情绪</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>痛点</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>机会点</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>感受说明</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="80" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>使用前</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>决定卖出闲置</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>浏览闲鱼首页推荐</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>整理家中闲置物品</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>闲鱼App、朋友推荐</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>这东西放着也是吃灰，不如卖点钱</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>首页推荐「一键转卖」引导</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="J2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3" ht="80" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>使用前</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>拍摄上传商品</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>拍照、编辑商品描述</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>闲鱼拍照工具</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>怎么拍才能让人想买呢？</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>拍照流程繁琐，没有引导模板</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>提供「智能识图+自动填描述」</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4" ht="80" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>使用中</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>与买家沟通</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>闲鱼聊天</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>闲鱼IM</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>这个人是不是真心想买？</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>沟通效率低，遇到砍价或骗子</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>AI辅助回复、信用分展示</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5" ht="80" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>使用中</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>达成交易</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>确认价格、发货地址</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>打包商品</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>闲鱼交易、快递</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>终于卖出去了，希望别出问题</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>担心买家收货后挑毛病</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>交易保障提示、纠纷快速处理</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6" ht="80" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>使用中</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>发货与物流</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>填写运单号</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>去快递点寄出</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>菜鸟裹裹、快递</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>运费比预期贵...</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>运费预估不准确，发货流程复杂</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>一键叫快递、运费补贴</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7" ht="80" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>使用后</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>买家确认收货</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>查看收款状态</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>闲鱼钱包、支付宝</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>钱到账了就好</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>到账时间有延迟感</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>实时到账提醒</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8" ht="80" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>使用后</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>评价与复购</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>写评价</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>闲鱼评价</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>整体还行，下次还会用</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>评价流程被动，缺乏激励</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>评价送优惠券、推荐类似商品</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -811,381 +929,381 @@
   <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>阶段区间</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>阶段名称</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>线上行为</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>线下行为</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>触点/渠道</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>用户想法</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>情绪</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>痛点</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>机会点</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>感受说明</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="80" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>使用前</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>产生购买需求</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>搜索关键词、浏览推荐</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>和朋友聊想买什么</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>闲鱼搜索、首页推荐</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>想找个便宜的二手XX，闲鱼上应该有</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>搜索联想、热门品类引导</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="J2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3" ht="80" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>使用前</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>筛选比较商品</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>对比价格、看成色、看卖家信用</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>闲鱼列表、商品详情</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>这个价格合理吗？这卖家靠谱吗？</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>商品信息不统一，真假难辨</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>标准化成色描述、验货服务</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4" ht="80" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>使用中</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>与卖家沟通</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>闲鱼聊天</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>闲鱼IM</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>能不能再便宜点？</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>议价过程耗时，怕被坑</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>合理议价引导、历史成交价参考</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5" ht="80" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>使用中</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>下单支付</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>点击购买、支付</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>支付宝</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>希望东西和描述一样</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>担保交易说明透明化</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6" ht="80" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>使用中</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>等待收货</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>查看物流进度</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>收快递</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>菜鸟裹裹、物流追踪</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>怎么还没到？</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>物流信息更新不及时</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>物流异常主动预警</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7" ht="80" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>使用后</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>验货与确认</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>确认收货</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>开箱检查商品</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>闲鱼确认收货</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>和描述一致，满意！</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>发现货不对版时维权流程复杂</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>「开箱验货」引导、快速维权</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8" ht="80" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>使用后</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>评价与分享</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>写评价、晒图</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>闲鱼评价、社交分享</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>买到好东西，推荐给朋友</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>分享路径长，缺乏晒单激励</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>一键生成晒单图、社区精选</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
